--- a/templates/economy-activities.xlsx
+++ b/templates/economy-activities.xlsx
@@ -4,11 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Оплата заданий" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Экономическая активность" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,18 +27,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,11 +43,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFEAE0"/>
+        <fgColor rgb="00EFEAE0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,20 +55,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,156 +428,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100.710625" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Шаблон: Оплата заданий</t>
+          <t>Шаблон: Экономическая активность</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Лист "Оплата заданий" — справочник оплаты заданий (Категория × Опасность × Эпоха →</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Лист "Экономическая активность" — ставки дохода/расхода в зм за день НА ОДНОГО ИГРОКА для</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>оплата партии в зм), которым мастер пользуется при подготовке к сессии. Admin-only —</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>партийных заданий и занятий в простое. Admin-only — игроки этот справочник не видят и на цены</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>обычная роль игрока эту таблицу не видит нигде (ни в каталоге, ни в расчёте цены</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>каталога он не влияет. Загружается на странице /admin/activities — импортируется только лист</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>предметов) и никак на неё не влияет. Загружается на странице /admin/quest-pay —</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>с точным названием "Экономическая активность".</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>импортируется только лист с точным названием "Оплата заданий".</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Колонки (строка 1 — заголовок, не трогать, данные — со строки 2):</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Колонки (строка 1 — заголовок, не трогать, данные — со строки 2):</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A: Тип — одно из: Задание, Простой</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A: Эпоха — одно из: I (1-4 ур.), II (5-10 ур.), III (11-16 ур.), IV (17-20 ур.)</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B: Категория — свободный текст: Дипломатия, Курьерские, Эскорт… для заданий;</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B: Категория — например, Дипломатия, Курьерские и логистика, Охота и зачистка,</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Практика профессии, Кутёж, Азартные игры… для простоя</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Расследования, Сбор и добыча, Спасение, Тайные операции, Труд и строительство,</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C: Опасность — только у заданий, одно из: Тривиальная, Лёгкая, Стандартная, Опасная,</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Экспедиции, Эскорт и охрана — свободный текст, список не фиксирован</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Смертельная. У простоя оставить пустым (если заполнено — игнорируется)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C: Опасность — одно из: Тривиальная, Лёгкая, Стандартная, Опасная, Смертельная</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D: Мин. уровень, E: Макс. уровень — целые 1..20, мин. не больше макс.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D: Задание — текст задания</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  F: Ставка мин, G: Ставка макс — зм/день на ОДНОГО игрока, всегда на игрока. Можно</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  E: Длительность — свободный текст, например "1-2 дня"</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     отрицательные (расход: обучение, кутёж). Мин. не больше макс.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  F: Оплата партии (зм) — целое число, оплата на партию целиком</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  H: Рек. длительность (дни) — целое ≥ 1, справочный ориентир</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  G: Примечание по балансу — свободный текст мастера</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  I: Описание — свободный текст</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Важное отличие от остальных шаблонов: у строк этого листа нет естественного ключа —</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  J: Примечание по балансу — свободный текст, можно пусто</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>несколько заданий одной Категории+Опасности+Эпохи допустимы, это не координата матрицы</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Выплата за контракт = Ставка × Рек. длительность, считается ОДИН РАЗ фиксированной суммой и</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>коэффициентов. Поэтому повторная загрузка НЕ обновляет записи по ключу, а полностью</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>не пересчитывается от фактически потраченных у стола дней (иначе затягивать выгоднее, чем</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>заменяет содержимое таблицы содержимым листа — то, чего нет в файле при очередной</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>работать быстро). Бонусы за скорость и штрафы за срыв сроков мастер назначает вручную.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>загрузке, будет удалено из базы.</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Строки с ошибками (нераспознанный тип/опасность, уровни или ставки не в порядке) пропускаются</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>с предупреждением, остальные загружаются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Важно: у строк этого листа нет естественного ключа — повторная загрузка НЕ обновляет записи</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>по ключу, а полностью заменяет содержимое таблицы содержимым листа: то, чего нет в файле,</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>будет удалено из базы.</t>
         </is>
       </c>
     </row>
@@ -605,50 +620,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Эпоха</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Опасность</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Задание</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Оплата партии (зм)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Мин. уровень</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Макс. уровень</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Ставка мин (зм/день на игрока)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Ставка макс (зм/день на игрока)</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Рек. длительность (дни)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Примечание по балансу</t>
         </is>
@@ -657,7 +690,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Задание</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,22 +703,66 @@
           <t>Тривиальная</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Доставить письмо старосте соседней деревни</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1 день</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Ознакомительное задание для новой партии</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ознакомительное задание</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Простой</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Кутёж</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Гулянка в таверне</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Расход, не доход</t>
         </is>
       </c>
     </row>
